--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:33:36+00:00</t>
+    <t>2025-02-26T15:37:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:37:29+00:00</t>
+    <t>2025-02-27T22:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="388">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T22:55:39+00:00</t>
+    <t>2025-03-02T19:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -836,10 +836,40 @@
     <t>RequestGroup.action.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.extension:structured-rating</t>
+  </si>
+  <si>
+    <t>structured-rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
+</t>
+  </si>
+  <si>
+    <t>PSS Rating Extension</t>
+  </si>
+  <si>
+    <t>A clinician-friendly rating, or score, for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>RequestGroup.action.modifierExtension</t>
@@ -942,6 +972,9 @@
   </si>
   <si>
     <t>RequestGroup.action.condition.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>RequestGroup.action.condition.modifierExtension</t>
@@ -1496,12 +1529,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.50390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="50.50390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1509,7 +1542,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.2890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="101.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4753,7 +4786,7 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4775,14 +4808,12 @@
         <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>134</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4819,19 +4850,17 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4852,19 +4881,21 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4877,26 +4908,22 @@
         <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>133</v>
+        <v>270</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4944,7 +4971,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4953,7 +4980,7 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>138</v>
@@ -4965,47 +4992,51 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5053,19 +5084,19 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
@@ -5074,15 +5105,15 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5108,10 +5139,10 @@
         <v>257</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5162,7 +5193,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5188,10 +5219,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5211,16 +5242,16 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>257</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5271,7 +5302,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5297,10 +5328,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5326,10 +5357,10 @@
         <v>257</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5380,7 +5411,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5406,10 +5437,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5429,16 +5460,16 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>199</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5465,13 +5496,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5489,7 +5520,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5504,7 +5535,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
@@ -5515,10 +5546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5529,7 +5560,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5541,13 +5572,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5574,13 +5605,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5598,13 +5629,13 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -5613,7 +5644,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
@@ -5624,10 +5655,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5650,13 +5681,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5707,7 +5738,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5722,7 +5753,7 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>291</v>
+        <v>211</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>77</v>
@@ -5733,10 +5764,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5759,17 +5790,15 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5818,7 +5847,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5833,7 +5862,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>77</v>
+        <v>300</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -5844,10 +5873,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5858,7 +5887,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -5870,15 +5899,17 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -5927,19 +5958,19 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -5948,26 +5979,26 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -5979,17 +6010,15 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6038,19 +6067,19 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -6064,14 +6093,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>266</v>
+        <v>132</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6084,26 +6113,24 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O42" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6151,7 +6178,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6172,49 +6199,51 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>130</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6238,13 +6267,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6262,19 +6291,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6283,15 +6312,15 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6299,7 +6328,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>87</v>
@@ -6314,16 +6343,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>306</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6349,13 +6378,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>77</v>
+        <v>313</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6373,10 +6402,10 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>87</v>
@@ -6399,10 +6428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6413,7 +6442,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6425,15 +6454,17 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>252</v>
+        <v>316</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6482,13 +6513,13 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
@@ -6508,10 +6539,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6522,7 +6553,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6534,13 +6565,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>259</v>
+        <v>322</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6591,19 +6622,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6612,26 +6643,26 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6643,17 +6674,15 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6702,19 +6731,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -6728,14 +6757,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>266</v>
+        <v>132</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6748,26 +6777,24 @@
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O48" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -6815,7 +6842,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6836,47 +6863,51 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>130</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -6924,19 +6955,19 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -6945,15 +6976,15 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6976,13 +7007,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7009,13 +7040,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>322</v>
+        <v>77</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7033,7 +7064,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -7059,10 +7090,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7070,7 +7101,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>87</v>
@@ -7085,13 +7116,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7118,13 +7149,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>77</v>
+        <v>332</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>333</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7142,10 +7173,10 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>87</v>
@@ -7168,10 +7199,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7194,13 +7225,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7251,7 +7282,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7266,7 +7297,7 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>332</v>
+        <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
@@ -7277,10 +7308,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7291,7 +7322,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7303,13 +7334,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7360,13 +7391,13 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
@@ -7375,10 +7406,10 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7386,10 +7417,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7400,7 +7431,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7412,13 +7443,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>207</v>
+        <v>344</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7445,37 +7476,37 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Z54" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -7484,10 +7515,10 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>77</v>
+        <v>347</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>77</v>
+        <v>348</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7495,10 +7526,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7521,13 +7552,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7554,31 +7585,31 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>184</v>
+        <v>352</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Z55" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7604,10 +7635,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7633,10 +7664,10 @@
         <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7666,10 +7697,10 @@
         <v>184</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -7687,7 +7718,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7713,10 +7744,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7742,10 +7773,10 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7775,10 +7806,10 @@
         <v>184</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -7796,7 +7827,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7822,10 +7853,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7851,10 +7882,10 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7884,10 +7915,10 @@
         <v>184</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -7905,7 +7936,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7931,10 +7962,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7960,10 +7991,10 @@
         <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7993,10 +8024,10 @@
         <v>184</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8014,7 +8045,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8040,10 +8071,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8066,17 +8097,15 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8101,13 +8130,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>379</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8125,7 +8154,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8134,7 +8163,7 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
@@ -8151,10 +8180,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8165,7 +8194,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8177,15 +8206,17 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8234,16 +8265,16 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>99</v>
@@ -8255,6 +8286,115 @@
         <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3316" uniqueCount="421">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -836,6 +836,365 @@
     <t>RequestGroup.action.extension</t>
   </si>
   <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.prefix</t>
+  </si>
+  <si>
+    <t>User-visible prefix for the action (e.g. 1. or A.)</t>
+  </si>
+  <si>
+    <t>A user-visible prefix for the action.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.title</t>
+  </si>
+  <si>
+    <t>User-visible title</t>
+  </si>
+  <si>
+    <t>The title of the action displayed to a user.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.description</t>
+  </si>
+  <si>
+    <t>Short description of the action</t>
+  </si>
+  <si>
+    <t>A short description of the action used to provide a summary to display to the user.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.textEquivalent</t>
+  </si>
+  <si>
+    <t>Static text equivalent of the action, used if the dynamic aspects cannot be interpreted by the receiving system</t>
+  </si>
+  <si>
+    <t>A text equivalent of the action to be performed. This provides a human-interpretable description of the action when the definition is consumed by a system that might not be capable of interpreting it dynamically.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.priority</t>
+  </si>
+  <si>
+    <t>Indicates how quickly the action should be addressed with respect to other actions.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.code</t>
+  </si>
+  <si>
+    <t>Code representing the meaning of the action or sub-actions</t>
+  </si>
+  <si>
+    <t>A code that provides meaning for the action or action group. For example, a section may have a LOINC code for a section of a documentation template.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelatedArtifact
+</t>
+  </si>
+  <si>
+    <t>Supporting documentation for the intended performer of the action</t>
+  </si>
+  <si>
+    <t>Didactic or other informational resources associated with the action that can be provided to the CDS recipient. Information resources can include inline text commentary and links to web resources.</t>
+  </si>
+  <si>
+    <t>Request.supportingInfo</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.condition</t>
+  </si>
+  <si>
+    <t>Whether or not the action is applicable</t>
+  </si>
+  <si>
+    <t>An expression that describes applicability criteria, or start/stop conditions for the action.</t>
+  </si>
+  <si>
+    <t>When multiple conditions of the same kind are present, the effects are combined using AND semantics, so the overall condition is true only if all of the conditions are true.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.condition.id</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.condition.extension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.condition.kind</t>
+  </si>
+  <si>
+    <t>applicability | start | stop</t>
+  </si>
+  <si>
+    <t>The kind of condition.</t>
+  </si>
+  <si>
+    <t>Applicability criteria are used to determine immediate applicability when a plan definition is applied to a given context. Start and stop criteria are carried through application and used to describe enter/exit criteria for an action.</t>
+  </si>
+  <si>
+    <t>The kind of condition for the action.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-condition-kind|4.0.1</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.condition.expression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expression
+</t>
+  </si>
+  <si>
+    <t>Boolean-valued expression</t>
+  </si>
+  <si>
+    <t>An expression that returns true or false, indicating whether or not the condition is satisfied.</t>
+  </si>
+  <si>
+    <t>The expression may be inlined, or may be a reference to a named expression within a logic library referenced by the library element.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.relatedAction</t>
+  </si>
+  <si>
+    <t>Relationship to another action</t>
+  </si>
+  <si>
+    <t>A relationship to another action such as "before" or "30-60 minutes after start of".</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.relatedAction.id</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.relatedAction.extension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.relatedAction.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.relatedAction.actionId</t>
+  </si>
+  <si>
+    <t>What action this is related to</t>
+  </si>
+  <si>
+    <t>The element id of the action this is related to.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.relatedAction.relationship</t>
+  </si>
+  <si>
+    <t>before-start | before | before-end | concurrent-with-start | concurrent | concurrent-with-end | after-start | after | after-end</t>
+  </si>
+  <si>
+    <t>The relationship of this action to the related action.</t>
+  </si>
+  <si>
+    <t>Defines the types of relationships between actions.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-relationship-type|4.0.1</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.relatedAction.offset[x]</t>
+  </si>
+  <si>
+    <t>Duration
+Range</t>
+  </si>
+  <si>
+    <t>Time offset for the relationship</t>
+  </si>
+  <si>
+    <t>A duration or range of durations to apply to the relationship. For example, 30-60 minutes before.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.timing[x]</t>
+  </si>
+  <si>
+    <t>dateTime
+AgePeriodDurationRangeTiming</t>
+  </si>
+  <si>
+    <t>When the action should take place</t>
+  </si>
+  <si>
+    <t>An optional value describing when the action should be performed.</t>
+  </si>
+  <si>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Device)
+</t>
+  </si>
+  <si>
+    <t>Who should perform the action</t>
+  </si>
+  <si>
+    <t>The participant that should perform or be responsible for this action.</t>
+  </si>
+  <si>
+    <t>Request.performer</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.type</t>
+  </si>
+  <si>
+    <t>create | update | remove | fire-event</t>
+  </si>
+  <si>
+    <t>The type of action to perform (create, update, remove).</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>The type of action to be performed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-type</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.groupingBehavior</t>
+  </si>
+  <si>
+    <t>visual-group | logical-group | sentence-group</t>
+  </si>
+  <si>
+    <t>Defines the grouping behavior for the action and its children.</t>
+  </si>
+  <si>
+    <t>Defines organization behavior of a group.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-grouping-behavior|4.0.1</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.selectionBehavior</t>
+  </si>
+  <si>
+    <t>any | all | all-or-none | exactly-one | at-most-one | one-or-more</t>
+  </si>
+  <si>
+    <t>Defines the selection behavior for the action and its children.</t>
+  </si>
+  <si>
+    <t>Defines selection behavior of a group.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-selection-behavior|4.0.1</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.requiredBehavior</t>
+  </si>
+  <si>
+    <t>must | could | must-unless-documented</t>
+  </si>
+  <si>
+    <t>Defines expectations around whether an action is required.</t>
+  </si>
+  <si>
+    <t>Defines expectations around whether an action or action group is required.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-required-behavior|4.0.1</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.precheckBehavior</t>
+  </si>
+  <si>
+    <t>yes | no</t>
+  </si>
+  <si>
+    <t>Defines whether the action should usually be preselected.</t>
+  </si>
+  <si>
+    <t>Defines selection frequency behavior for an action or group.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-precheck-behavior|4.0.1</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.cardinalityBehavior</t>
+  </si>
+  <si>
+    <t>single | multiple</t>
+  </si>
+  <si>
+    <t>Defines whether the action can be selected multiple times.</t>
+  </si>
+  <si>
+    <t>Defines behavior for an action or a group for how many times that item may be repeated.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-cardinality-behavior|4.0.1</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.resource</t>
+  </si>
+  <si>
+    <t>The target of the action</t>
+  </si>
+  <si>
+    <t>The resource that is the target of the action (e.g. CommunicationRequest).</t>
+  </si>
+  <si>
+    <t>The target resource SHALL be a [Request](http://hl7.org/fhir/R4/request.html) resource with a Request.intent set to "option".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rqg-1
+</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action</t>
+  </si>
+  <si>
+    <t>Sub action</t>
+  </si>
+  <si>
+    <t>Sub actions.</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.id</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.extension</t>
+  </si>
+  <si>
     <t>Extension</t>
   </si>
   <si>
@@ -849,10 +1208,7 @@
     <t>open</t>
   </si>
   <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.extension:structured-rating</t>
+    <t>RequestGroup.action.action.extension:structured-rating</t>
   </si>
   <si>
     <t>structured-rating</t>
@@ -872,354 +1228,97 @@
 </t>
   </si>
   <si>
-    <t>RequestGroup.action.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.prefix</t>
-  </si>
-  <si>
-    <t>User-visible prefix for the action (e.g. 1. or A.)</t>
-  </si>
-  <si>
-    <t>A user-visible prefix for the action.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.title</t>
-  </si>
-  <si>
-    <t>User-visible title</t>
-  </si>
-  <si>
-    <t>The title of the action displayed to a user.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.description</t>
-  </si>
-  <si>
-    <t>Short description of the action</t>
-  </si>
-  <si>
-    <t>A short description of the action used to provide a summary to display to the user.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.textEquivalent</t>
-  </si>
-  <si>
-    <t>Static text equivalent of the action, used if the dynamic aspects cannot be interpreted by the receiving system</t>
-  </si>
-  <si>
-    <t>A text equivalent of the action to be performed. This provides a human-interpretable description of the action when the definition is consumed by a system that might not be capable of interpreting it dynamically.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.priority</t>
-  </si>
-  <si>
-    <t>Indicates how quickly the action should be addressed with respect to other actions.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.code</t>
-  </si>
-  <si>
-    <t>Code representing the meaning of the action or sub-actions</t>
-  </si>
-  <si>
-    <t>A code that provides meaning for the action or action group. For example, a section may have a LOINC code for a section of a documentation template.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.documentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelatedArtifact
-</t>
-  </si>
-  <si>
-    <t>Supporting documentation for the intended performer of the action</t>
-  </si>
-  <si>
-    <t>Didactic or other informational resources associated with the action that can be provided to the CDS recipient. Information resources can include inline text commentary and links to web resources.</t>
-  </si>
-  <si>
-    <t>Request.supportingInfo</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.condition</t>
-  </si>
-  <si>
-    <t>Whether or not the action is applicable</t>
-  </si>
-  <si>
-    <t>An expression that describes applicability criteria, or start/stop conditions for the action.</t>
-  </si>
-  <si>
-    <t>When multiple conditions of the same kind are present, the effects are combined using AND semantics, so the overall condition is true only if all of the conditions are true.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.condition.id</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.condition.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.condition.modifierExtension</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.condition.kind</t>
-  </si>
-  <si>
-    <t>applicability | start | stop</t>
-  </si>
-  <si>
-    <t>The kind of condition.</t>
-  </si>
-  <si>
-    <t>Applicability criteria are used to determine immediate applicability when a plan definition is applied to a given context. Start and stop criteria are carried through application and used to describe enter/exit criteria for an action.</t>
-  </si>
-  <si>
-    <t>The kind of condition for the action.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/action-condition-kind|4.0.1</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.condition.expression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expression
-</t>
-  </si>
-  <si>
-    <t>Boolean-valued expression</t>
-  </si>
-  <si>
-    <t>An expression that returns true or false, indicating whether or not the condition is satisfied.</t>
-  </si>
-  <si>
-    <t>The expression may be inlined, or may be a reference to a named expression within a logic library referenced by the library element.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.relatedAction</t>
-  </si>
-  <si>
-    <t>Relationship to another action</t>
-  </si>
-  <si>
-    <t>A relationship to another action such as "before" or "30-60 minutes after start of".</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.relatedAction.id</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.relatedAction.extension</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.relatedAction.modifierExtension</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.relatedAction.actionId</t>
-  </si>
-  <si>
-    <t>What action this is related to</t>
-  </si>
-  <si>
-    <t>The element id of the action this is related to.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.relatedAction.relationship</t>
-  </si>
-  <si>
-    <t>before-start | before | before-end | concurrent-with-start | concurrent | concurrent-with-end | after-start | after | after-end</t>
-  </si>
-  <si>
-    <t>The relationship of this action to the related action.</t>
-  </si>
-  <si>
-    <t>Defines the types of relationships between actions.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/action-relationship-type|4.0.1</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.relatedAction.offset[x]</t>
-  </si>
-  <si>
-    <t>Duration
-Range</t>
-  </si>
-  <si>
-    <t>Time offset for the relationship</t>
-  </si>
-  <si>
-    <t>A duration or range of durations to apply to the relationship. For example, 30-60 minutes before.</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.timing[x]</t>
-  </si>
-  <si>
-    <t>dateTime
-AgePeriodDurationRangeTiming</t>
-  </si>
-  <si>
-    <t>When the action should take place</t>
-  </si>
-  <si>
-    <t>An optional value describing when the action should be performed.</t>
-  </si>
-  <si>
-    <t>Request.occurrence[x]</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Device)
-</t>
-  </si>
-  <si>
-    <t>Who should perform the action</t>
-  </si>
-  <si>
-    <t>The participant that should perform or be responsible for this action.</t>
-  </si>
-  <si>
-    <t>Request.performer</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.type</t>
-  </si>
-  <si>
-    <t>create | update | remove | fire-event</t>
-  </si>
-  <si>
-    <t>The type of action to perform (create, update, remove).</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>The type of action to be performed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/action-type</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.groupingBehavior</t>
-  </si>
-  <si>
-    <t>visual-group | logical-group | sentence-group</t>
-  </si>
-  <si>
-    <t>Defines the grouping behavior for the action and its children.</t>
-  </si>
-  <si>
-    <t>Defines organization behavior of a group.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/action-grouping-behavior|4.0.1</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.selectionBehavior</t>
-  </si>
-  <si>
-    <t>any | all | all-or-none | exactly-one | at-most-one | one-or-more</t>
-  </si>
-  <si>
-    <t>Defines the selection behavior for the action and its children.</t>
-  </si>
-  <si>
-    <t>Defines selection behavior of a group.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/action-selection-behavior|4.0.1</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.requiredBehavior</t>
-  </si>
-  <si>
-    <t>must | could | must-unless-documented</t>
-  </si>
-  <si>
-    <t>Defines expectations around whether an action is required.</t>
-  </si>
-  <si>
-    <t>Defines expectations around whether an action or action group is required.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/action-required-behavior|4.0.1</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.precheckBehavior</t>
-  </si>
-  <si>
-    <t>yes | no</t>
-  </si>
-  <si>
-    <t>Defines whether the action should usually be preselected.</t>
-  </si>
-  <si>
-    <t>Defines selection frequency behavior for an action or group.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/action-precheck-behavior|4.0.1</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.cardinalityBehavior</t>
-  </si>
-  <si>
-    <t>single | multiple</t>
-  </si>
-  <si>
-    <t>Defines whether the action can be selected multiple times.</t>
-  </si>
-  <si>
-    <t>Defines behavior for an action or a group for how many times that item may be repeated.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/action-cardinality-behavior|4.0.1</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.resource</t>
-  </si>
-  <si>
-    <t>The target of the action</t>
-  </si>
-  <si>
-    <t>The resource that is the target of the action (e.g. CommunicationRequest).</t>
-  </si>
-  <si>
-    <t>The target resource SHALL be a [Request](http://hl7.org/fhir/R4/request.html) resource with a Request.intent set to "option".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rqg-1
-</t>
-  </si>
-  <si>
-    <t>RequestGroup.action.action</t>
-  </si>
-  <si>
-    <t>Sub action</t>
-  </si>
-  <si>
-    <t>Sub actions.</t>
+    <t>RequestGroup.action.action.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.prefix</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.title</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.description</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.textEquivalent</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.priority</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.code</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.documentation</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.id</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.extension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.kind</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.condition.expression</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.id</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.extension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.modifierExtension</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.actionId</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.relationship</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.relatedAction.offset[x]</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.timing[x]</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.participant</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.type</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.groupingBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.selectionBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.requiredBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.precheckBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.cardinalityBehavior</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.resource</t>
+  </si>
+  <si>
+    <t>RequestGroup.action.action.action</t>
   </si>
 </sst>
 </file>
@@ -1529,11 +1628,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.50390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.50390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="56.73046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -4572,10 +4671,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4786,7 +4885,7 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4808,12 +4907,14 @@
         <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N30" s="2"/>
+      <c r="N30" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4850,17 +4951,19 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4881,21 +4984,19 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4908,22 +5009,26 @@
         <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>270</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4971,7 +5076,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4980,7 +5085,7 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>138</v>
@@ -4992,51 +5097,47 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5084,19 +5185,19 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
@@ -5105,15 +5206,15 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5139,10 +5240,10 @@
         <v>257</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5193,7 +5294,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5219,10 +5320,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5242,16 +5343,16 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>257</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5302,7 +5403,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5328,10 +5429,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5357,10 +5458,10 @@
         <v>257</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5411,7 +5512,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5437,10 +5538,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5460,16 +5561,16 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>257</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>199</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5496,13 +5597,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5520,7 +5621,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5535,7 +5636,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
@@ -5546,10 +5647,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5560,7 +5661,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5572,13 +5673,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>199</v>
+        <v>285</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5605,13 +5706,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5629,13 +5730,13 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -5644,7 +5745,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
@@ -5655,10 +5756,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5681,13 +5782,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>207</v>
+        <v>288</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5738,7 +5839,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5753,7 +5854,7 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>211</v>
+        <v>291</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>77</v>
@@ -5764,10 +5865,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5790,15 +5891,17 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5847,7 +5950,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5862,7 +5965,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -5873,10 +5976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5887,7 +5990,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -5899,17 +6002,15 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>302</v>
+        <v>258</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -5958,19 +6059,19 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -5979,26 +6080,26 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6010,15 +6111,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6067,19 +6170,19 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -6093,14 +6196,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>132</v>
+        <v>266</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6113,24 +6216,26 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6178,7 +6283,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6199,51 +6304,49 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>261</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6267,13 +6370,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6291,19 +6394,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6312,15 +6415,15 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6328,7 +6431,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>87</v>
@@ -6343,16 +6446,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>306</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6378,13 +6481,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>313</v>
+        <v>77</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>314</v>
+        <v>77</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6402,10 +6505,10 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>87</v>
@@ -6428,10 +6531,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6442,7 +6545,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6454,17 +6557,15 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>316</v>
+        <v>252</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6513,13 +6614,13 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
@@ -6539,10 +6640,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6553,7 +6654,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6565,13 +6666,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>321</v>
+        <v>258</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>322</v>
+        <v>259</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6622,19 +6723,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6643,26 +6744,26 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6674,15 +6775,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6731,19 +6834,19 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -6757,14 +6860,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>132</v>
+        <v>266</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6777,24 +6880,26 @@
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -6842,7 +6947,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6863,51 +6968,47 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>261</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -6955,19 +7056,19 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -6976,15 +7077,15 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7007,13 +7108,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7040,13 +7141,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>322</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>77</v>
+        <v>323</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7064,7 +7165,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -7090,10 +7191,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7101,7 +7202,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>87</v>
@@ -7116,13 +7217,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7149,13 +7250,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>332</v>
+        <v>77</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>333</v>
+        <v>77</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7173,10 +7274,10 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>87</v>
@@ -7199,10 +7300,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7225,13 +7326,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7282,7 +7383,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7297,7 +7398,7 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>77</v>
+        <v>332</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
@@ -7308,10 +7409,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7322,7 +7423,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7334,13 +7435,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7391,13 +7492,13 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
@@ -7406,10 +7507,10 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7417,10 +7518,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7431,7 +7532,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7443,13 +7544,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>344</v>
+        <v>207</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7476,13 +7577,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>77</v>
+        <v>344</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7500,13 +7601,13 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -7515,10 +7616,10 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>348</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7526,10 +7627,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7552,13 +7653,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7585,13 +7686,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>352</v>
+        <v>184</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7609,7 +7710,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7635,10 +7736,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7664,10 +7765,10 @@
         <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7697,10 +7798,10 @@
         <v>184</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -7718,7 +7819,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7744,10 +7845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7773,10 +7874,10 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7806,10 +7907,10 @@
         <v>184</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -7827,7 +7928,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7853,10 +7954,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7882,10 +7983,10 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7915,10 +8016,10 @@
         <v>184</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -7936,7 +8037,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7962,10 +8063,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7991,10 +8092,10 @@
         <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8024,10 +8125,10 @@
         <v>184</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8045,7 +8146,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8071,10 +8172,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8097,15 +8198,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8130,13 +8233,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>379</v>
+        <v>77</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8154,7 +8257,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8163,7 +8266,7 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
@@ -8180,10 +8283,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8194,7 +8297,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8206,17 +8309,15 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8265,16 +8366,16 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>99</v>
@@ -8291,10 +8392,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8305,7 +8406,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8317,13 +8418,13 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>386</v>
+        <v>258</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>387</v>
+        <v>259</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8374,27 +8475,3648 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AC63" s="2"/>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C64" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI62" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AK66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseRequestGroup</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseRequestGroup</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1214,7 +1214,7 @@
     <t>structured-rating</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSStructuredRating}
 </t>
   </si>
   <si>
@@ -1641,7 +1641,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="101.08984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.93359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:59:35+00:00</t>
+    <t>2025-03-07T09:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:27:46+00:00</t>
+    <t>2025-03-11T13:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-11T13:27:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:29:42+00:00</t>
+    <t>2025-03-17T15:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17T15:05:50+00:00</t>
+    <t>2025-03-18T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:04:30+00:00</t>
+    <t>2025-03-20T11:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T11:13:27+00:00</t>
+    <t>2025-03-20T15:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T15:00:12+00:00</t>
+    <t>2025-03-24T10:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:58:19+00:00</t>
+    <t>2025-03-24T11:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:08+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-03-24T12:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T12:21:29+00:00</t>
+    <t>2025-03-26T10:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-26T10:25:04+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T06:02:42+00:00</t>
+    <t>2025-04-10T08:21:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-10T08:21:04+00:00</t>
+    <t>2025-04-15T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-15T15:53:54+00:00</t>
+    <t>2025-04-16T11:48:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:10+00:00</t>
+    <t>2025-04-16T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,22 +57,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:51+00:00</t>
+    <t>2025-04-16T12:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:31:30+00:00</t>
+    <t>2025-04-16T12:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:36:28+00:00</t>
+    <t>2025-04-16T12:41:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:41:18+00:00</t>
+    <t>2025-04-16T13:08:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,22 +57,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T13:08:49+00:00</t>
+    <t>2025-04-17T08:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>HL7 Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:21:49+00:00</t>
+    <t>2025-04-17T08:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1631,17 +1631,17 @@
   <dimension ref="A1:AM95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.73046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.63671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.63671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.28515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.53125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1650,25 +1650,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="83.765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="71.81640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.32421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T08:44:33+00:00</t>
+    <t>2025-04-17T09:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:22:19+00:00</t>
+    <t>2025-04-17T09:39:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:39:14+00:00</t>
+    <t>2025-04-17T11:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,22 +57,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T11:28:46+00:00</t>
+    <t>2025-04-28T07:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:14+00:00</t>
+    <t>2025-04-28T07:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:51+00:00</t>
+    <t>2025-04-28T07:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:00+00:00</t>
+    <t>2025-04-28T07:57:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:33+00:00</t>
+    <t>2025-04-28T07:57:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:44+00:00</t>
+    <t>2025-04-30T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:13:57+00:00</t>
+    <t>2025-04-30T14:16:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:07+00:00</t>
+    <t>2025-04-30T14:16:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:39+00:00</t>
+    <t>2025-05-06T09:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T09:47:23+00:00</t>
+    <t>2025-05-06T11:05:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T11:05:16+00:00</t>
+    <t>2025-05-06T11:11:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T11:11:40+00:00</t>
+    <t>2025-05-12T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:14:30+00:00</t>
+    <t>2025-05-12T19:48:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -680,7 +680,7 @@
     <t>RequestGroup.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSPatient)
 </t>
   </si>
   <si>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:50:51+00:00</t>
+    <t>2025-05-12T19:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:54:00+00:00</t>
+    <t>2025-05-13T10:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:10+00:00</t>
+    <t>2025-05-13T10:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:30+00:00</t>
+    <t>2025-05-13T11:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:53:59+00:00</t>
+    <t>2025-05-13T11:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:54:01+00:00</t>
+    <t>2025-05-13T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:55:17+00:00</t>
+    <t>2025-05-14T06:43:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:43:44+00:00</t>
+    <t>2025-05-14T06:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:09+00:00</t>
+    <t>2025-05-14T06:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:38+00:00</t>
+    <t>2025-05-14T06:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:56:25+00:00</t>
+    <t>2025-05-14T07:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:28:26+00:00</t>
+    <t>2025-05-14T07:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:16+00:00</t>
+    <t>2025-05-14T07:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:17+00:00</t>
+    <t>2025-05-14T07:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:38:16+00:00</t>
+    <t>2025-05-14T07:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:51:32+00:00</t>
+    <t>2025-05-14T07:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:52:33+00:00</t>
+    <t>2025-05-14T07:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:53:22+00:00</t>
+    <t>2025-05-14T08:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:06:44+00:00</t>
+    <t>2025-05-14T08:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:53:34+00:00</t>
+    <t>2025-05-14T08:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:54:50+00:00</t>
+    <t>2025-05-14T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:05:29+00:00</t>
+    <t>2025-05-14T13:37:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:37:41+00:00</t>
+    <t>2025-05-14T14:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:59:57+00:00</t>
+    <t>2025-05-14T15:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:00:45+00:00</t>
+    <t>2025-05-14T15:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:07:35+00:00</t>
+    <t>2025-05-14T15:08:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -63,22 +63,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T15:08:16+00:00</t>
+    <t>2025-05-22T14:06:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:43:01+00:00</t>
+    <t>2025-05-22T14:52:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T14:52:21+00:00</t>
+    <t>2025-06-11T04:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T04:00:37+00:00</t>
+    <t>2025-06-26T13:57:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T13:57:34+00:00</t>
+    <t>2025-07-16T16:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PSSResponseRequestGroup.xlsx
+++ b/StructureDefinition-PSSResponseRequestGroup.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T16:47:23+00:00</t>
+    <t>2025-07-16T16:49:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
